--- a/data_lake/reporte_cordoba_mes/dt=2026-08-04/CORDOBA_AGO26.xlsx
+++ b/data_lake/reporte_cordoba_mes/dt=2026-08-04/CORDOBA_AGO26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8290E8-A8D1-4328-B7DF-90C6CC396647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6046B1FF-1B17-4325-9AED-A7037E647D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F8F14AC-D557-4126-B18A-7A2C1E69122F}"/>
   </bookViews>
@@ -9966,7 +9966,7 @@
                   <c:v>2.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1</c:v>
+                  <c:v>150.20000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-1</c:v>
@@ -19925,7 +19925,9 @@
       <c r="F3" s="24">
         <v>0</v>
       </c>
-      <c r="G3" s="25"/>
+      <c r="G3" s="25">
+        <v>0</v>
+      </c>
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25"/>
@@ -19981,7 +19983,9 @@
       <c r="F4" s="24">
         <v>0</v>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="25">
+        <v>0</v>
+      </c>
       <c r="H4" s="25"/>
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
@@ -20037,7 +20041,9 @@
       <c r="F5" s="24">
         <v>2.1</v>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="25">
+        <v>16.399999999999999</v>
+      </c>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
@@ -20068,7 +20074,7 @@
       <c r="AI5" s="34"/>
       <c r="AJ5" s="36">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>20</v>
       </c>
       <c r="AK5" s="30">
         <v>40.986206896551728</v>
@@ -20093,7 +20099,9 @@
       <c r="F6" s="24">
         <v>0</v>
       </c>
-      <c r="G6" s="25"/>
+      <c r="G6" s="25">
+        <v>34.5</v>
+      </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
@@ -20124,7 +20132,7 @@
       <c r="AI6" s="34"/>
       <c r="AJ6" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="AK6" s="30">
         <v>88.719230769230762</v>
@@ -20253,7 +20261,9 @@
       <c r="F9" s="24">
         <v>0</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="25">
+        <v>28</v>
+      </c>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="J9" s="25"/>
@@ -20284,7 +20294,7 @@
       <c r="AI9" s="34"/>
       <c r="AJ9" s="36">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AK9" s="30">
         <v>65.482758620689651</v>
@@ -20359,7 +20369,9 @@
       <c r="F11" s="24">
         <v>0</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="25">
+        <v>3.2</v>
+      </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="J11" s="25"/>
@@ -20390,7 +20402,7 @@
       <c r="AI11" s="34"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK11" s="30">
         <v>19.188461538461539</v>
@@ -20411,7 +20423,9 @@
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
-      <c r="G12" s="25"/>
+      <c r="G12" s="25">
+        <v>0</v>
+      </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
@@ -20467,7 +20481,9 @@
       <c r="F13" s="24">
         <v>0</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="25">
+        <v>0</v>
+      </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
       <c r="J13" s="25"/>
@@ -20521,7 +20537,9 @@
       <c r="F14" s="24">
         <v>0</v>
       </c>
-      <c r="G14" s="25"/>
+      <c r="G14" s="25">
+        <v>49.5</v>
+      </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
       <c r="J14" s="25"/>
@@ -20552,7 +20570,7 @@
       <c r="AI14" s="34"/>
       <c r="AJ14" s="36">
         <f>SUM(E14:AI14)</f>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="AK14" s="30">
         <v>36.1</v>
@@ -20575,7 +20593,9 @@
       <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="25">
+        <v>18.600000000000001</v>
+      </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="J15" s="25"/>
@@ -20606,7 +20626,7 @@
       <c r="AI15" s="34"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="AK15" s="30">
         <v>60.46</v>
@@ -20724,7 +20744,7 @@
       </c>
       <c r="G19" s="26">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>150.20000000000002</v>
       </c>
       <c r="H19" s="26">
         <f t="shared" si="1"/>
